--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6024-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6024-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD454754-B5FA-4E49-B9B4-93A439A638C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{12795CB8-C9EA-402B-9BF3-CCF8FCB4C85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{F1BBEF64-530A-4433-A6FB-9CA95E4FFB39}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{0748ACDB-9D70-4D95-A1B3-502633A57B64}"/>
   </bookViews>
   <sheets>
     <sheet name="6024-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1553,29 +1553,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9B6ED04-D581-43B0-89DA-C7F8D03FA2BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{033A5C0F-6EA5-4E79-AD74-D7CA7DAAA5F6}">
   <dimension ref="A1:X34"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1609,7 +1608,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1645,7 +1644,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1697,7 +1696,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1765,7 +1764,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1837,7 +1836,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1909,7 +1908,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -1981,7 +1980,7 @@
         <v>8.2899999999999991</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2053,7 +2052,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2125,7 +2124,7 @@
         <v>7.74</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2197,7 +2196,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2269,7 +2268,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="42">
         <v>2017</v>
       </c>
@@ -2341,7 +2340,7 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="44"/>
       <c r="B13" s="45"/>
       <c r="C13" s="19" t="s">
@@ -2369,7 +2368,7 @@
       <c r="W13" s="53"/>
       <c r="X13" s="47"/>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="38">
         <v>2016</v>
       </c>
@@ -2441,7 +2440,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="40">
         <v>2015</v>
       </c>
@@ -2513,7 +2512,7 @@
         <v>8.61</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="54">
         <v>2014</v>
       </c>
@@ -2585,7 +2584,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="56"/>
       <c r="B17" s="57"/>
       <c r="C17" s="21" t="s">
@@ -2613,7 +2612,7 @@
       <c r="W17" s="63"/>
       <c r="X17" s="59"/>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2013</v>
       </c>
@@ -2685,7 +2684,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2012</v>
       </c>
@@ -2757,7 +2756,7 @@
         <v>6.68</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2011</v>
       </c>
@@ -2829,7 +2828,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="54">
         <v>2010</v>
       </c>
@@ -2901,7 +2900,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="56"/>
       <c r="B22" s="57"/>
       <c r="C22" s="21" t="s">
@@ -2929,7 +2928,7 @@
       <c r="W22" s="63"/>
       <c r="X22" s="59"/>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="42">
         <v>2009</v>
       </c>
@@ -3001,7 +3000,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="44"/>
       <c r="B24" s="45"/>
       <c r="C24" s="19" t="s">
@@ -3029,7 +3028,7 @@
       <c r="W24" s="53"/>
       <c r="X24" s="47"/>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2008</v>
       </c>
@@ -3101,7 +3100,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <v>2007</v>
       </c>
@@ -3173,7 +3172,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2006</v>
       </c>
@@ -3245,7 +3244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2005</v>
       </c>
@@ -3317,7 +3316,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2004</v>
       </c>
@@ -3389,7 +3388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>2003</v>
       </c>
@@ -3461,7 +3460,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2002</v>
       </c>
@@ -3533,7 +3532,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>2001</v>
       </c>
@@ -3605,7 +3604,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>2000</v>
       </c>
@@ -3677,7 +3676,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="40" t="s">
         <v>50</v>
       </c>
